--- a/server/src/data/西班牙语单词本-名词.xlsx
+++ b/server/src/data/西班牙语单词本-名词.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的项目\业务mvp\vocabulario-espanol\server\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370C342A-68BC-4F57-895F-E093294D1DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4CC9DC-16DB-40D1-8DD4-5BF0802507AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31635" yWindow="2310" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34545" yWindow="2070" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="名词表" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="533">
   <si>
     <t>原形</t>
   </si>
@@ -54,10 +54,10 @@
     <t>montaña（原形）</t>
   </si>
   <si>
-    <t>山将几个世纪的记忆藏于岩石</t>
-  </si>
-  <si>
-    <t>La montaña guarda siglos de memoria en sus rocas</t>
+    <t>他山将几个世纪的记忆藏于岩石。</t>
+  </si>
+  <si>
+    <t>La montaña guarda siglos de memoria en sus rocas.</t>
   </si>
   <si>
     <t>阴性名词；复数montañas；搭配：subir una montaña爬山</t>
@@ -69,13 +69,13 @@
     <t>森林</t>
   </si>
   <si>
-    <t>bosque（原形）</t>
-  </si>
-  <si>
-    <t>森林用沙沙声讲述着四季的故事</t>
-  </si>
-  <si>
-    <t>El bosque cuenta historias de las estaciones con su susurro</t>
+    <t>bosque（原形） | 阴阳性同形: Bosque</t>
+  </si>
+  <si>
+    <t>他森林用沙沙声讲述着四季的故事。</t>
+  </si>
+  <si>
+    <t>El bosque cuenta historias de las estaciones con su susurro.</t>
   </si>
   <si>
     <t>阳性名词；复数bosques；搭配：entrar en el bosque进入森林</t>
@@ -90,10 +90,10 @@
     <t>playa（原形）</t>
   </si>
   <si>
-    <t>海滩收藏着每一朵浪花的温柔</t>
-  </si>
-  <si>
-    <t>La playa guarda la ternura de cada ola</t>
+    <t>他海滩收藏着每一朵浪花的温柔。</t>
+  </si>
+  <si>
+    <t>La playa guarda la ternura de cada ola.</t>
   </si>
   <si>
     <t>阴性名词；复数playas；搭配：ir a la playa去海滩</t>
@@ -105,13 +105,13 @@
     <t>国家</t>
   </si>
   <si>
-    <t>país（原形）</t>
-  </si>
-  <si>
-    <t>在危机时期，国家依赖州与州之间的团结</t>
-  </si>
-  <si>
-    <t>En tiempos de crisis, el pais depende de la solidaridad entre estados</t>
+    <t>país（原形） | 阴阳性同形: Pais</t>
+  </si>
+  <si>
+    <t>他在危机时期，国家依赖州与州之间的团结。</t>
+  </si>
+  <si>
+    <t>Él En tiempos de crisis, el pais depende de la solidaridad entre estados.</t>
   </si>
   <si>
     <t>阳性名词；复数países；搭配：viajar por el país周游全国</t>
@@ -123,13 +123,13 @@
     <t>州/状态</t>
   </si>
   <si>
-    <t>estados（原形）</t>
-  </si>
-  <si>
-    <t>国家依赖州与州之间的团结</t>
-  </si>
-  <si>
-    <t>la solidaridad entre estados</t>
+    <t>estados（原形） | 阳性: Estado | 阴性: Estada</t>
+  </si>
+  <si>
+    <t>他国家依赖州与州之间的团结。</t>
+  </si>
+  <si>
+    <t>Él la solidaridad entre estados.</t>
   </si>
   <si>
     <t>阳性名词；复数estados；多义词：州/状态/国家</t>
@@ -141,13 +141,13 @@
     <t>群体</t>
   </si>
   <si>
-    <t>grupo（原形）</t>
-  </si>
-  <si>
-    <t>以及每个群体的承诺</t>
-  </si>
-  <si>
-    <t>y del compromiso de cada grupo</t>
+    <t>grupo（原形） | 阳性: Grupo | 阴性: Grupa</t>
+  </si>
+  <si>
+    <t>他以及每个群体的承诺。</t>
+  </si>
+  <si>
+    <t>Él y del compromiso de cada grupo.</t>
   </si>
   <si>
     <t>阳性名词；复数grupos；搭配：un grupo de一群</t>
@@ -159,13 +159,13 @@
     <t>工作</t>
   </si>
   <si>
-    <t>trabajo（原形）</t>
-  </si>
-  <si>
-    <t>而工作把每一分钟都转化为旋律</t>
-  </si>
-  <si>
-    <t>y el trabajo transforma cada minuto en melodía</t>
+    <t>trabajo（原形） | 阳性: Trabajo | 阴性: Trabaja</t>
+  </si>
+  <si>
+    <t>他而工作把每一分钟都转化为旋律。</t>
+  </si>
+  <si>
+    <t>Él y el trabajo transforma cada minuto en melodía.</t>
   </si>
   <si>
     <t>阳性名词；复数trabajos；搭配：ir al trabajo去上班</t>
@@ -180,10 +180,10 @@
     <t>lugar（原形）</t>
   </si>
   <si>
-    <t>每个地方都有其独特的节奏</t>
-  </si>
-  <si>
-    <t>Cada lugar tiene un ritmo propio</t>
+    <t>他每个地方都有其独特的节奏。</t>
+  </si>
+  <si>
+    <t>Él Cada lugar tiene un ritmo propio.</t>
   </si>
   <si>
     <t>阳性名词；复数lugares；搭配：en cualquier lugar在任何地方</t>
@@ -195,13 +195,7 @@
     <t>分钟</t>
   </si>
   <si>
-    <t>minuto（原形）</t>
-  </si>
-  <si>
-    <t>而工作把每一分钟都转化为旋律</t>
-  </si>
-  <si>
-    <t>y el trabajo transforma cada minuto en melodía</t>
+    <t>minuto（原形） | 阳性: Minuto | 阴性: Minuta</t>
   </si>
   <si>
     <t>阳性名词；复数minutos；搭配：cada minuto每分钟</t>
@@ -216,10 +210,10 @@
     <t>mujer（原形）</t>
   </si>
   <si>
-    <t>一个以敏锐目光注视着小镇的女人</t>
-  </si>
-  <si>
-    <t>Una mujer que observa con ojo perspicaz el pueblo</t>
+    <t>他一个以敏锐目光注视着小镇的女人。</t>
+  </si>
+  <si>
+    <t>Él Una mujer que observa con ojo perspicaz el pueblo.</t>
   </si>
   <si>
     <t>阴性名词；复数mujeres；搭配：una mujer joven年轻女性</t>
@@ -231,13 +225,13 @@
     <t>村庄</t>
   </si>
   <si>
-    <t>pueblo（原形）</t>
-  </si>
-  <si>
-    <t>注视着小镇的女人</t>
-  </si>
-  <si>
-    <t>observa con ojo perspicaz el pueblo</t>
+    <t>pueblo（原形） | 阳性: Pueblo | 阴性: Puebla</t>
+  </si>
+  <si>
+    <t>他注视着小镇的女人。</t>
+  </si>
+  <si>
+    <t>Él observa con ojo perspicaz el pueblo.</t>
   </si>
   <si>
     <t>阳性名词；复数pueblos；搭配：un pueblo pequeño小村庄</t>
@@ -249,13 +243,7 @@
     <t>眼睛</t>
   </si>
   <si>
-    <t>ojo（原形）</t>
-  </si>
-  <si>
-    <t>一个以敏锐目光注视着小镇的女人</t>
-  </si>
-  <si>
-    <t>Una mujer que observa con ojo perspicaz el pueblo</t>
+    <t>ojo（原形） | 阳性: Ojo | 阴性: Oja</t>
   </si>
   <si>
     <t>阳性名词；复数ojos；搭配：con los ojos abiertos睁着眼睛</t>
@@ -270,10 +258,10 @@
     <t>vida（原形）</t>
   </si>
   <si>
-    <t>在他生命中留下无形且不可磨灭的印记</t>
-  </si>
-  <si>
-    <t>deja una huella invisible en su vida</t>
+    <t>在他生命中留下无形且不可磨灭的印记。</t>
+  </si>
+  <si>
+    <t>Él deja una huella invisible en su vida.</t>
   </si>
   <si>
     <t>阴性名词；复数vidas；搭配：toda la vida一生</t>
@@ -285,13 +273,13 @@
     <t>手</t>
   </si>
   <si>
-    <t>mano（原形）</t>
-  </si>
-  <si>
-    <t>那只抚摸孩子的手</t>
-  </si>
-  <si>
-    <t>La mano que acaricia al nifno</t>
+    <t>mano（原形） | 阳性: Mano | 阴性: Mana</t>
+  </si>
+  <si>
+    <t>他那只抚摸孩子的手。</t>
+  </si>
+  <si>
+    <t>La mano que acaricia al nifno.</t>
   </si>
   <si>
     <t>阴性名词；复数manos；搭配：con las manos en el bolsillo双手插兜</t>
@@ -303,13 +291,7 @@
     <t>孩子</t>
   </si>
   <si>
-    <t>niño（原形）</t>
-  </si>
-  <si>
-    <t>那只抚摸孩子的手</t>
-  </si>
-  <si>
-    <t>La mano que acaricia al nifno</t>
+    <t>niño（原形） | 阳性: Nino | 阴性: Nina</t>
   </si>
   <si>
     <t>阳性名词；复数niños；搭配：un niño pequeño小孩子</t>
@@ -321,13 +303,13 @@
     <t>年</t>
   </si>
   <si>
-    <t>año（原形）</t>
-  </si>
-  <si>
-    <t>岁月在不经意间流逝</t>
-  </si>
-  <si>
-    <t>los anos corren sin aviso</t>
+    <t>año（原形） | 阳性: Ano | 阴性: Ana</t>
+  </si>
+  <si>
+    <t>他岁月在不经意间流逝。</t>
+  </si>
+  <si>
+    <t>Él los anos corren sin aviso.</t>
   </si>
   <si>
     <t>阳性名词；复数años；搭配：cada año每年</t>
@@ -342,10 +324,10 @@
     <t>día（原形）</t>
   </si>
   <si>
-    <t>而每一天都提醒着我们</t>
-  </si>
-  <si>
-    <t>y cada día nos recuerda que todo cambia</t>
+    <t>而每一天都提醒着我们。</t>
+  </si>
+  <si>
+    <t>Él y cada día nos recuerda que todo cambia.</t>
   </si>
   <si>
     <t>阳性名词；复数días；搭配：todos los días每天</t>
@@ -357,13 +339,13 @@
     <t>世界</t>
   </si>
   <si>
-    <t>mundo（原形）</t>
-  </si>
-  <si>
-    <t>世界不停地旋转</t>
-  </si>
-  <si>
-    <t>EI mundo gira sin detenerse</t>
+    <t>mundo（原形） | 阳性: Mundo | 阴性: Munda</t>
+  </si>
+  <si>
+    <t>他世界不停地旋转。</t>
+  </si>
+  <si>
+    <t>El mundo gira sin detenerse.</t>
   </si>
   <si>
     <t>阳性名词；复数mundos；搭配：en todo el mundo全世界</t>
@@ -378,10 +360,10 @@
     <t>casa（原形）</t>
   </si>
   <si>
-    <t>在一座时间仿佛静止的房子里</t>
-  </si>
-  <si>
-    <t>En una casa donde el tiempo parece detenerse</t>
+    <t>在一座时间仿佛静止的房子里。</t>
+  </si>
+  <si>
+    <t>Él En una casa donde el tiempo parece detenerse.</t>
   </si>
   <si>
     <t>阴性名词；复数casas；搭配：en casa在家</t>
@@ -393,13 +375,7 @@
     <t>时间</t>
   </si>
   <si>
-    <t>tiempo（原形）</t>
-  </si>
-  <si>
-    <t>在一座时间仿佛静止的房子里</t>
-  </si>
-  <si>
-    <t>En una casa donde el tiempo parece detenerse</t>
+    <t>tiempo（原形） | 阳性: Tiempo | 阴性: Tiempa</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：perder el tiempo浪费时间</t>
@@ -411,13 +387,13 @@
     <t>人</t>
   </si>
   <si>
-    <t>hombre（原形）</t>
-  </si>
-  <si>
-    <t>人明白真正的财富不在墙壁之间</t>
-  </si>
-  <si>
-    <t>el hombre aprende que la verdadera riqueza no está en las paredes</t>
+    <t>hombre（原形） | 阴阳性同形: Hombre</t>
+  </si>
+  <si>
+    <t>他人明白真正的财富不在墙壁之间。</t>
+  </si>
+  <si>
+    <t>El hombre aprende que la verdadera riqueza no está en las paredes.</t>
   </si>
   <si>
     <t>阳性名词；复数hombres；搭配：un hombre de negocios商人</t>
@@ -429,13 +405,13 @@
     <t>上司</t>
   </si>
   <si>
-    <t>jefe（原形）</t>
-  </si>
-  <si>
-    <t>一位好的上司就像一所流动的大学</t>
-  </si>
-  <si>
-    <t>Un buen jefe es como una universidad ambulante</t>
+    <t>jefe（原形） | 阴阳性同形: Jefe</t>
+  </si>
+  <si>
+    <t>他一位好的上司就像一所流动的大学。</t>
+  </si>
+  <si>
+    <t>Él Un buen jefe es como una universidad ambulante.</t>
   </si>
   <si>
     <t>阳性名词；复数jefes；搭配：el jefe de departamento部门主管</t>
@@ -447,13 +423,13 @@
     <t>学生</t>
   </si>
   <si>
-    <t>estudiante（原形）</t>
-  </si>
-  <si>
-    <t>而每个项目都是一堂课，在那里我们每个人都是学生</t>
-  </si>
-  <si>
-    <t>y cada proyecto es una clase donde todos somos estudiantes</t>
+    <t>estudiante（原形） | 阴阳性同形: Estudiante</t>
+  </si>
+  <si>
+    <t>而每个项目都是一堂课，在那里我们每个人都是学生。</t>
+  </si>
+  <si>
+    <t>Él y cada proyecto es una clase donde todos somos estudiantes.</t>
   </si>
   <si>
     <t>阳性/阴性名词；复数estudiantes；搭配：un estudiante de universidad大学生</t>
@@ -465,13 +441,7 @@
     <t>大学</t>
   </si>
   <si>
-    <t>universidad（原形）</t>
-  </si>
-  <si>
-    <t>一位好的上司就像一所流动的大学</t>
-  </si>
-  <si>
-    <t>Un buen jefe es como una universidad ambulante</t>
+    <t>universidad（原形） | 阴性名词: Universidad</t>
   </si>
   <si>
     <t>阴性名词；复数universidades；搭配：ir a la universidad上大学</t>
@@ -483,13 +453,13 @@
     <t>父亲</t>
   </si>
   <si>
-    <t>padre（原形）</t>
-  </si>
-  <si>
-    <t>我的父亲从未向我讲述他的故事</t>
-  </si>
-  <si>
-    <t>Mi padre nunca me contó su historia</t>
+    <t>padre（原形） | 阴阳性同形: Padre</t>
+  </si>
+  <si>
+    <t>我的父亲从未向我讲述他的故事。</t>
+  </si>
+  <si>
+    <t>Él Mi padre nunca me contó su historia.</t>
   </si>
   <si>
     <t>阳性名词；复数padres；搭配：mi padre我的父亲</t>
@@ -501,13 +471,13 @@
     <t>道路</t>
   </si>
   <si>
-    <t>camino（原形）</t>
-  </si>
-  <si>
-    <t>但我从他弯下的脊背和教会我行走的道路上读懂了它</t>
-  </si>
-  <si>
-    <t>pero la aprendí en cada curva de su espalda y en el camino que me enseno a caminar</t>
+    <t>camino（原形） | 阳性: Camino | 阴性: Camina</t>
+  </si>
+  <si>
+    <t>但我从他弯下的脊背和教会我行走的道路上读懂了它。</t>
+  </si>
+  <si>
+    <t>Él pero la aprendí en cada curva de su espalda y en el camino que me enseno a caminar.</t>
   </si>
   <si>
     <t>阳性名词；复数caminos；搭配：en el camino在路上</t>
@@ -522,12 +492,6 @@
     <t>historia（原形）</t>
   </si>
   <si>
-    <t>我的父亲从未向我讲述他的故事</t>
-  </si>
-  <si>
-    <t>Mi padre nunca me contó su historia</t>
-  </si>
-  <si>
     <t>阴性名词；复数historias；搭配：contar una historia讲故事</t>
   </si>
   <si>
@@ -540,10 +504,10 @@
     <t>sistema（原形）</t>
   </si>
   <si>
-    <t>在夜晚寂静的星系里</t>
-  </si>
-  <si>
-    <t>En el silencioso sistema de la noche</t>
+    <t>他在夜晚寂静的星系里。</t>
+  </si>
+  <si>
+    <t>Él En el silencioso sistema de la noche.</t>
   </si>
   <si>
     <t>阳性名词；复数sistemas；搭配：un sistema operativo操作系统</t>
@@ -555,13 +519,13 @@
     <t>朋友</t>
   </si>
   <si>
-    <t>amigo（原形）</t>
-  </si>
-  <si>
-    <t>一位朋友是指引我前行的星辰</t>
-  </si>
-  <si>
-    <t>un amigo es la constelación que guía mi camino</t>
+    <t>amigo（原形） | 阳性: Amigo | 阴性: Amiga</t>
+  </si>
+  <si>
+    <t>一位朋友是指引我前行的星辰。</t>
+  </si>
+  <si>
+    <t>Él un amigo es la constelación que guía mi camino.</t>
   </si>
   <si>
     <t>阳性名词；复数amigos；搭配：un amigo cercano亲密的朋友</t>
@@ -573,13 +537,13 @@
     <t>母亲</t>
   </si>
   <si>
-    <t>madre（原形）</t>
-  </si>
-  <si>
-    <t>而母亲的回声，是无言拥抱我的月光</t>
-  </si>
-  <si>
-    <t>y el eco de mi madre es la luna que me abraza sin palabras</t>
+    <t>madre（原形） | 阴阳性同形: Madre</t>
+  </si>
+  <si>
+    <t>而母亲的回声，是无言拥抱我的月光。</t>
+  </si>
+  <si>
+    <t>Él y el eco de mi madre es la luna que me abraza sin palabras.</t>
   </si>
   <si>
     <t>阴性名词；复数madres；搭配：mi madre我的母亲</t>
@@ -591,13 +555,13 @@
     <t>点</t>
   </si>
   <si>
-    <t>punto（原形）</t>
-  </si>
-  <si>
-    <t>这具身体是我能称之为"我"的宇宙唯一之点</t>
-  </si>
-  <si>
-    <t>el dolor no era un final, sino el punto donde todo recomienza</t>
+    <t>punto（原形） | 阳性: Punto | 阴性: Punta</t>
+  </si>
+  <si>
+    <t>这具身体是我能称之为"我"的宇宙唯一之点。</t>
+  </si>
+  <si>
+    <t>El dolor no era un final, sino El punto donde todo recomienza.</t>
   </si>
   <si>
     <t>阳性名词；复数puntos；搭配：un punto de vista观点</t>
@@ -609,13 +573,10 @@
     <t>身体</t>
   </si>
   <si>
-    <t>cuerpo（原形）</t>
-  </si>
-  <si>
-    <t>这具身体是我能称之为"我"的宇宙唯一之点</t>
-  </si>
-  <si>
-    <t>Llegó un momento en que todo mi cuerpo comprendió la verdad</t>
+    <t>cuerpo（原形） | 阳性: Cuerpo | 阴性: Cuerpa</t>
+  </si>
+  <si>
+    <t>Él Llegó un momento en que todo mi cuerpo comprendió la verdad.</t>
   </si>
   <si>
     <t>阳性名词；复数cuerpos；搭配：el cuerpo humano人体</t>
@@ -627,13 +588,10 @@
     <t>时刻</t>
   </si>
   <si>
-    <t>momento（原形）</t>
-  </si>
-  <si>
-    <t>而在这觉醒的时刻，整个宇宙都在我体内显现</t>
-  </si>
-  <si>
-    <t>Llegó un momento en que todo mi cuerpo comprendió la verdad</t>
+    <t>momento（原形） | 阳性: Momento | 阴性: Momenta</t>
+  </si>
+  <si>
+    <t>而在这觉醒的时刻，整个宇宙都在我体内显现。</t>
   </si>
   <si>
     <t>阳性名词；复数momentos；搭配：en este momento此刻</t>
@@ -645,13 +603,13 @@
     <t>情况</t>
   </si>
   <si>
-    <t>caso（原形）</t>
-  </si>
-  <si>
-    <t>在冲突的情况下</t>
-  </si>
-  <si>
-    <t>En caso de conflicto</t>
+    <t>caso（原形） | 阳性: Caso | 阴性: Casa</t>
+  </si>
+  <si>
+    <t>他在冲突的情况下。</t>
+  </si>
+  <si>
+    <t>Él En caso de conflicto.</t>
   </si>
   <si>
     <t>阳性名词；复数casos；搭配：en caso de如果</t>
@@ -666,10 +624,10 @@
     <t>forma（原形）</t>
   </si>
   <si>
-    <t>与家人沟通的方式</t>
-  </si>
-  <si>
-    <t>la forma de comunicarnos con nuestra familia</t>
+    <t>他与家人沟通的方式。</t>
+  </si>
+  <si>
+    <t>Él la forma de comunicarnos con nuestra familia.</t>
   </si>
   <si>
     <t>阴性名词；复数formas；搭配：de esta forma用这种方式</t>
@@ -684,12 +642,6 @@
     <t>familia（原形）</t>
   </si>
   <si>
-    <t>与家人沟通的方式</t>
-  </si>
-  <si>
-    <t>la forma de comunicarnos con nuestra familia</t>
-  </si>
-  <si>
     <t>阴性名词；复数familias；搭配：mi familia我的家庭</t>
   </si>
   <si>
@@ -699,13 +651,13 @@
     <t>部分</t>
   </si>
   <si>
-    <t>parte（原形）</t>
-  </si>
-  <si>
-    <t>生活由小小的部分和简单的事物组成</t>
-  </si>
-  <si>
-    <t>la vida está hecha de pequenas partes y cosas simples</t>
+    <t>parte（原形） | 阴阳性同形: Parte</t>
+  </si>
+  <si>
+    <t>生活由小小的部分和简单的事物组成。</t>
+  </si>
+  <si>
+    <t>Él la vida está hecha de pequenas partes y cosas simples.</t>
   </si>
   <si>
     <t>阴性名词；复数partes；搭配：una parte de一部分</t>
@@ -720,12 +672,6 @@
     <t>cosa（原形）</t>
   </si>
   <si>
-    <t>生活由小小的部分和简单的事物组成</t>
-  </si>
-  <si>
-    <t>la vida está hecha de pequenas partes y cosas simples</t>
-  </si>
-  <si>
     <t>阴性名词；复数cosas；搭配：cosas simples简单的事物</t>
   </si>
   <si>
@@ -735,13 +681,13 @@
     <t>月份</t>
   </si>
   <si>
-    <t>mes（原形）</t>
-  </si>
-  <si>
-    <t>每个月都提醒我们</t>
-  </si>
-  <si>
-    <t>Cada mes nos recuerda que</t>
+    <t>mes（原形） | 阴阳性同形: Mes</t>
+  </si>
+  <si>
+    <t>每个月都提醒我们。</t>
+  </si>
+  <si>
+    <t>Él Cada mes nos recuerda que.</t>
   </si>
   <si>
     <t>阳性名词；复数meses；搭配：cada mes每个月</t>
@@ -756,10 +702,10 @@
     <t>tierra（原形）</t>
   </si>
   <si>
-    <t>怀着敬畏触摸土地</t>
-  </si>
-  <si>
-    <t>Tocar la tierra con reverencia</t>
+    <t>他怀着敬畏触摸土地。</t>
+  </si>
+  <si>
+    <t>Él Tocar la tierra con reverencia.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la tierra地球/土地</t>
@@ -771,13 +717,13 @@
     <t>神</t>
   </si>
   <si>
-    <t>dios（原形）</t>
-  </si>
-  <si>
-    <t>或许是感受神的一种方式</t>
-  </si>
-  <si>
-    <t>puede ser una forma de sentir a dios</t>
+    <t>dios（原形） | 阴阳性同形: Dios</t>
+  </si>
+  <si>
+    <t>他或许是感受神的一种方式。</t>
+  </si>
+  <si>
+    <t>Él puede ser una forma de sentir a dios.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：Dios上帝</t>
@@ -789,13 +735,13 @@
     <t>意义</t>
   </si>
   <si>
-    <t>sentido（原形）</t>
-  </si>
-  <si>
-    <t>许多人找到了归属于宇宙的意义</t>
-  </si>
-  <si>
-    <t>muchas personas encuentran el sentido_de pertenencia al universo</t>
+    <t>sentido（原形） | 阳性: Sentido | 阴性: Sentida</t>
+  </si>
+  <si>
+    <t>他许多人找到了归属于宇宙的意义。</t>
+  </si>
+  <si>
+    <t>Él muchas personas encuentran el sentido_de pertenencia al universo.</t>
   </si>
   <si>
     <t>阳性名词；复数sentidos；搭配：el sentido de la vida生命的意义</t>
@@ -807,13 +753,13 @@
     <t>城市</t>
   </si>
   <si>
-    <t>ciudad（原形）</t>
-  </si>
-  <si>
-    <t>树木在水泥丛中生长，见证着城市如何点亮灯火</t>
-  </si>
-  <si>
-    <t>El arbol crece entre el cemento, testigo de cómo la ciudad enciende sus luces</t>
+    <t>ciudad（原形） | 阴性名词: Ciudad</t>
+  </si>
+  <si>
+    <t>他树木在水泥丛中生长，见证着城市如何点亮灯火。</t>
+  </si>
+  <si>
+    <t>El arbol crece entre el cemento, testigo de cómo la ciudad enciende sus luces.</t>
   </si>
   <si>
     <t>阴性名词；复数ciudades；搭配：la ciudad城市</t>
@@ -825,13 +771,13 @@
     <t>树木</t>
   </si>
   <si>
-    <t>árbol（原形）</t>
-  </si>
-  <si>
-    <t>树木在水泥丛中生长</t>
-  </si>
-  <si>
-    <t>El arbol crece entre el cemento</t>
+    <t>árbol（原形） | 阴阳性同形: Arbol</t>
+  </si>
+  <si>
+    <t>他树木在水泥丛中生长。</t>
+  </si>
+  <si>
+    <t>El arbol crece entre el cemento.</t>
   </si>
   <si>
     <t>阳性名词；复数árboles；搭配：un árbol de manzana苹果树</t>
@@ -843,13 +789,13 @@
     <t>夜晚</t>
   </si>
   <si>
-    <t>noche（原形）</t>
-  </si>
-  <si>
-    <t>对抗夜晚的帷幕</t>
-  </si>
-  <si>
-    <t>contra el manto de la noche</t>
+    <t>noche（原形） | 阴阳性同形: Noche</t>
+  </si>
+  <si>
+    <t>他对抗夜晚的帷幕。</t>
+  </si>
+  <si>
+    <t>Él contra el manto de la noche.</t>
   </si>
   <si>
     <t>阴性名词；复数noches；搭配：de noche在晚上</t>
@@ -861,13 +807,13 @@
     <t>出生/诞生</t>
   </si>
   <si>
-    <t>nacimiento（原形）</t>
-  </si>
-  <si>
-    <t>随着我的诞生，我收到了两份礼物</t>
-  </si>
-  <si>
-    <t>Con mi nacimiento, recibi dos regalos</t>
+    <t>nacimiento（原形） | 阳性: Nacimiento | 阴性: Nacimienta</t>
+  </si>
+  <si>
+    <t>随着我的诞生，我收到了两份礼物。</t>
+  </si>
+  <si>
+    <t>Él Con mi nacimiento, recibi dos regalos.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：el nacimiento de un bebé婴儿的出生</t>
@@ -882,10 +828,10 @@
     <t>estrella（原形）</t>
   </si>
   <si>
-    <t>拥有第一颗星星的天空</t>
-  </si>
-  <si>
-    <t>el cielo con su primera estrella</t>
+    <t>他拥有第一颗星星的天空。</t>
+  </si>
+  <si>
+    <t>El ciElo con su primera estrElla.</t>
   </si>
   <si>
     <t>阴性名词；复数estrellas；搭配：las estrellas星星</t>
@@ -897,13 +843,13 @@
     <t>狗</t>
   </si>
   <si>
-    <t>perro（原形）</t>
-  </si>
-  <si>
-    <t>一只教会我何为无条件的爱的忠犬</t>
-  </si>
-  <si>
-    <t>un perro fiel que me ensenó sobre el amor incondicional</t>
+    <t>perro（原形） | 阳性: Perro | 阴性: Perra</t>
+  </si>
+  <si>
+    <t>一只教会我何为无条件的爱的忠犬。</t>
+  </si>
+  <si>
+    <t>Él un perro fiel que me ensenó sobre el amor incondicional.</t>
   </si>
   <si>
     <t>阳性名词；复数perros；搭配：un perro fiel忠实的狗</t>
@@ -915,13 +861,13 @@
     <t>河流</t>
   </si>
   <si>
-    <t>río（原形）</t>
-  </si>
-  <si>
-    <t>每一个被我们遗忘的名字，都是一颗沉入遗忘之河的石头</t>
-  </si>
-  <si>
-    <t>Cada nombre que olvidamos es una piedra que se hunde en el rio del olvido</t>
+    <t>río（原形） | 阳性: Rio | 阴性: Ria</t>
+  </si>
+  <si>
+    <t>每一个被我们遗忘的名字，都是一颗沉入遗忘之河的石头。</t>
+  </si>
+  <si>
+    <t>Él Cada nombre que olvidamos es una piedra que se hunde en el rio del olvido.</t>
   </si>
   <si>
     <t>阳性名词；复数ríos；搭配：el río河流</t>
@@ -933,13 +879,13 @@
     <t>人们</t>
   </si>
   <si>
-    <t>personas（原形）</t>
-  </si>
-  <si>
-    <t>带走了无数人们的故事</t>
-  </si>
-  <si>
-    <t>llevándose consigo la historia de innumerables personas</t>
+    <t>personas（原形） | 阴阳性同形: Personas</t>
+  </si>
+  <si>
+    <t>带走了无数人们的故事。</t>
+  </si>
+  <si>
+    <t>Él llevándose consigo la historia de innumerables personas.</t>
   </si>
   <si>
     <t>阴性名词；复数personas；搭配：muchas personas很多人</t>
@@ -951,13 +897,13 @@
     <t>名字</t>
   </si>
   <si>
-    <t>nombre（原形）</t>
-  </si>
-  <si>
-    <t>每一个被我们遗忘的名字</t>
-  </si>
-  <si>
-    <t>Cada nombre que olvidamos</t>
+    <t>nombre（原形） | 阴阳性同形: Nombre</t>
+  </si>
+  <si>
+    <t>每一个被我们遗忘的名字。</t>
+  </si>
+  <si>
+    <t>Él Cada nombre que olvidamos.</t>
   </si>
   <si>
     <t>阳性名词；复数nombres；搭配：mi nombre我的名字</t>
@@ -969,13 +915,13 @@
     <t>政府</t>
   </si>
   <si>
-    <t>gobierno（原形）</t>
-  </si>
-  <si>
-    <t>推动着政府试图管理的经济</t>
-  </si>
-  <si>
-    <t>impulsando la economia que el gobierno busca administrar</t>
+    <t>gobierno（原形） | 阳性: Gobierno | 阴性: Gobierna</t>
+  </si>
+  <si>
+    <t>他推动着政府试图管理的经济。</t>
+  </si>
+  <si>
+    <t>Él impulsando la economia que el gobierno busca administrar.</t>
   </si>
   <si>
     <t>阳性名词；复数gobiernos；搭配：el gobierno政府</t>
@@ -990,10 +936,10 @@
     <t>compañía（原形）</t>
   </si>
   <si>
-    <t>一家有远见的公司如同奔流向海的江河</t>
-  </si>
-  <si>
-    <t>Una companía visionaria es como un rio que fluye hacia el mar</t>
+    <t>他一家有远见的公司如同奔流向海的江河。</t>
+  </si>
+  <si>
+    <t>Él Una companía visionaria es como un rio que fluye hacia el mar.</t>
   </si>
   <si>
     <t>阴性名词；复数compañías；搭配：una empresa公司</t>
@@ -1008,12 +954,6 @@
     <t>mar（原形）</t>
   </si>
   <si>
-    <t>一家有远见的公司如同奔流向海的江河</t>
-  </si>
-  <si>
-    <t>Una companía visionaria es como un rio que fluye hacia el mar</t>
-  </si>
-  <si>
     <t>阳性名词；不可数；搭配：el mar海洋</t>
   </si>
   <si>
@@ -1026,10 +966,10 @@
     <t>fin（原形）</t>
   </si>
   <si>
-    <t>它的基石不是法律，而是那些不知斗争何时是终点的劳动者的汗水</t>
-  </si>
-  <si>
-    <t>el sudor del trabajador_que no conoce el fin de su lucha</t>
+    <t>它的基石不是法律，而是那些不知斗争何时是终点的劳动者的汗水。</t>
+  </si>
+  <si>
+    <t>El sudor dEl trabajador_que no conoce El fin de su lucha.</t>
   </si>
   <si>
     <t>阳性名词；复数fines；搭配：el fin de la lucha斗争的终点</t>
@@ -1041,13 +981,10 @@
     <t>工人</t>
   </si>
   <si>
-    <t>trabajador（原形）</t>
-  </si>
-  <si>
-    <t>而是那些不知斗争何时是终点的劳动者的汗水</t>
-  </si>
-  <si>
-    <t>el sudor del trabajador_que no conoce el fin de su lucha</t>
+    <t>trabajador（原形） | 阳性: Trabajador | 阴性: Trabajadora</t>
+  </si>
+  <si>
+    <t>他而是那些不知斗争何时是终点的劳动者的汗水。</t>
   </si>
   <si>
     <t>阳性名词；复数trabajadores；搭配：un trabajador工人</t>
@@ -1059,13 +996,13 @@
     <t>项目/规划</t>
   </si>
   <si>
-    <t>proyecto（原形）</t>
-  </si>
-  <si>
-    <t>在梦想的蓝图与达成的现实之间</t>
-  </si>
-  <si>
-    <t>Entre el proyecto sonado y la realidad lograda</t>
+    <t>proyecto（原形） | 阳性: Proyecto | 阴性: Proyecta</t>
+  </si>
+  <si>
+    <t>他在梦想的蓝图与达成的现实之间。</t>
+  </si>
+  <si>
+    <t>Él Entre el proyecto sonado y la realidad lograda.</t>
   </si>
   <si>
     <t>阳性名词；复数proyectos；搭配：un proyecto项目</t>
@@ -1074,16 +1011,13 @@
     <t>Gente</t>
   </si>
   <si>
-    <t>人们</t>
-  </si>
-  <si>
-    <t>gente（原形）</t>
-  </si>
-  <si>
-    <t>有一座唯有人们能用自己的努力与希望建造的桥梁</t>
-  </si>
-  <si>
-    <t>hay un puente que solo la gente puede construir con su esfuerzo y esperanza</t>
+    <t>gente（原形） | 阴阳性同形: Gente</t>
+  </si>
+  <si>
+    <t>有一座唯有人们能用自己的努力与希望建造的桥梁。</t>
+  </si>
+  <si>
+    <t>Él hay un puente que solo la gente puede construir con su esfuerzo y esperanza.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la gente人们</t>
@@ -1095,13 +1029,7 @@
     <t>现实</t>
   </si>
   <si>
-    <t>realidad（原形）</t>
-  </si>
-  <si>
-    <t>在梦想的蓝图与达成的现实之间</t>
-  </si>
-  <si>
-    <t>Entre el proyecto sonado y la realidad lograda</t>
+    <t>realidad（原形） | 阴性名词: Realidad</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la realidad现实</t>
@@ -1116,10 +1044,10 @@
     <t>cabeza（原形）</t>
   </si>
   <si>
-    <t>头脑置于星空</t>
-  </si>
-  <si>
-    <t>la cabeza en las estrellas</t>
+    <t>他头脑置于星空。</t>
+  </si>
+  <si>
+    <t>Él la cabeza en las estrellas.</t>
   </si>
   <si>
     <t>阴性名词；复数cabezas；搭配：la cabeza头</t>
@@ -1131,13 +1059,13 @@
     <t>脚</t>
   </si>
   <si>
-    <t>pie（原形）</t>
-  </si>
-  <si>
-    <t>双脚踏于实地</t>
-  </si>
-  <si>
-    <t>Con los pies en la tierra</t>
+    <t>pie（原形） | 阴阳性同形: Pie</t>
+  </si>
+  <si>
+    <t>他双脚踏于实地。</t>
+  </si>
+  <si>
+    <t>Él Con los pies en la tierra.</t>
   </si>
   <si>
     <t>阳性名词；复数pies；搭配：los pies脚</t>
@@ -1152,10 +1080,10 @@
     <t>área（原形）</t>
   </si>
   <si>
-    <t>两者之间的这片空间</t>
-  </si>
-  <si>
-    <t>el área entre ambos</t>
+    <t>他两者之间的这片空间。</t>
+  </si>
+  <si>
+    <t>El área entre ambos.</t>
   </si>
   <si>
     <t>阴性名词；复数áreas；搭配：un área区域</t>
@@ -1164,16 +1092,13 @@
     <t>Hogar</t>
   </si>
   <si>
-    <t>家</t>
-  </si>
-  <si>
     <t>hogar（原形）</t>
   </si>
   <si>
-    <t>我渴望的真正头衔不在我的名片上，而在于成为我家的建筑师</t>
-  </si>
-  <si>
-    <t>EI verdadero titulo que anhelo no está en mi tarjeta de presentación, sino en ser el arquitecto de mi hogar</t>
+    <t>我渴望的真正头衔不在我的名片上，而在于成为我家的建筑师。</t>
+  </si>
+  <si>
+    <t>El verdadero titulo que anhelo no está en mi tarjeta de presentación, sino en ser el arquitecto de mi hogar.</t>
   </si>
   <si>
     <t>阳性名词；复数hogares；搭配：mi hogar我的家</t>
@@ -1185,13 +1110,13 @@
     <t>创造</t>
   </si>
   <si>
-    <t>creación（原形）</t>
-  </si>
-  <si>
-    <t>以及一段充满爱的家族历史的创造者</t>
-  </si>
-  <si>
-    <t>la creación de una historia familiar llena de amor</t>
+    <t>creación（原形） | 阳性: Creación | 阴性: Creacina</t>
+  </si>
+  <si>
+    <t>他以及一段充满爱的家族历史的创造者。</t>
+  </si>
+  <si>
+    <t>Él la creación de una historia familiar llena de amor.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la creación创造</t>
@@ -1203,13 +1128,13 @@
     <t>头衔</t>
   </si>
   <si>
-    <t>título（原形）</t>
-  </si>
-  <si>
-    <t>我渴望的真正头衔不在我的名片上</t>
-  </si>
-  <si>
-    <t>EI verdadero titulo que anhelo no está en mi tarjeta de presentación</t>
+    <t>título（原形） | 阳性: Titulo | 阴性: Titula</t>
+  </si>
+  <si>
+    <t>我渴望的真正头衔不在我的名片上。</t>
+  </si>
+  <si>
+    <t>El verdadero titulo que anhelo no está en mi tarjeta de presentación.</t>
   </si>
   <si>
     <t>阳性名词；复数títulos；搭配：un título头衔</t>
@@ -1221,13 +1146,13 @@
     <t>太阳</t>
   </si>
   <si>
-    <t>sol（原形）</t>
-  </si>
-  <si>
-    <t>太阳赐予的每一个黎明</t>
-  </si>
-  <si>
-    <t>Cada amanecer que regala el sol</t>
+    <t>sol（原形） | 阴阳性同形: Sol</t>
+  </si>
+  <si>
+    <t>他太阳赐予的每一个黎明。</t>
+  </si>
+  <si>
+    <t>Él Cada amanecer que regala el sol.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：el sol太阳</t>
@@ -1242,31 +1167,19 @@
     <t>semana（原形）</t>
   </si>
   <si>
-    <t>都标志着一个充满可能的新星期的开始</t>
-  </si>
-  <si>
-    <t>marca el inicio de una nueva semana de posibilidades</t>
+    <t>他都标志着一个充满可能的新星期的开始。</t>
+  </si>
+  <si>
+    <t>Él marca el inicio de una nueva semana de posibilidades.</t>
   </si>
   <si>
     <t>阴性名词；复数semanas；搭配：cada semana每个星期</t>
   </si>
   <si>
-    <t>Mes</t>
-  </si>
-  <si>
-    <t>月份</t>
-  </si>
-  <si>
-    <t>mes（原形）</t>
-  </si>
-  <si>
-    <t>而在每个月的末尾</t>
-  </si>
-  <si>
-    <t>al final de cada mes</t>
-  </si>
-  <si>
-    <t>阳性名词；复数meses；搭配：cada mes每个月</t>
+    <t>他而在每个月的末尾。</t>
+  </si>
+  <si>
+    <t>Él al final de cada mes.</t>
   </si>
   <si>
     <t>Luna</t>
@@ -1278,10 +1191,10 @@
     <t>luna（原形）</t>
   </si>
   <si>
-    <t>如同月亮教会潮汐它永恒的节奏</t>
-  </si>
-  <si>
-    <t>como la luna ensena a las mareas su eterno ritmo</t>
+    <t>如同月亮教会潮汐它永恒的节奏。</t>
+  </si>
+  <si>
+    <t>Él como la luna ensena a las mareas su eterno ritmo.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la luna月亮</t>
@@ -1293,13 +1206,13 @@
     <t>儿子</t>
   </si>
   <si>
-    <t>hijo（原形）</t>
-  </si>
-  <si>
-    <t>我教会儿子如何在这个世界航行</t>
-  </si>
-  <si>
-    <t>Le enseno a mi hijo a navegar este mundo</t>
+    <t>hijo（原形） | 阳性: Hijo | 阴性: Hija</t>
+  </si>
+  <si>
+    <t>我教会儿子如何在这个世界航行。</t>
+  </si>
+  <si>
+    <t>Él Le enseno a mi hijo a navegar este mundo.</t>
   </si>
   <si>
     <t>阳性名词；复数hijos；搭配：mi hijo我的儿子</t>
@@ -1314,10 +1227,10 @@
     <t>política（原形）</t>
   </si>
   <si>
-    <t>在历史的车站里，政治如匆忙旅客般上下权力列车</t>
-  </si>
-  <si>
-    <t>En la estación de la historia, la politica sube y baja del poder como pasajeros apresurados</t>
+    <t>他在历史的车站里，政治如匆忙旅客般上下权力列车。</t>
+  </si>
+  <si>
+    <t>Él En la estación de la historia, la politica sube y baja del poder como pasajeros apresurados.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la política政治</t>
@@ -1329,13 +1242,13 @@
     <t>车站</t>
   </si>
   <si>
-    <t>estación（原形）</t>
-  </si>
-  <si>
-    <t>在历史的车站里</t>
-  </si>
-  <si>
-    <t>En la estación de la historia</t>
+    <t>estación（原形） | 阳性: Estación | 阴性: Estacina</t>
+  </si>
+  <si>
+    <t>他在历史的车站里。</t>
+  </si>
+  <si>
+    <t>Él En la estación de la historia.</t>
   </si>
   <si>
     <t>阴性名词；复数estaciones；搭配：la estación de tren火车站</t>
@@ -1350,10 +1263,10 @@
     <t>iglesia（原形）</t>
   </si>
   <si>
-    <t>而教堂仍是凝视火车离去的古老穹顶</t>
-  </si>
-  <si>
-    <t>mientras la iglesia permanece como la boveda antigua que observa los trenes partir</t>
+    <t>他而教堂仍是凝视火车离去的古老穹顶。</t>
+  </si>
+  <si>
+    <t>Él mientras la iglesia permanece como la boveda antigua que observa los trenes partir.</t>
   </si>
   <si>
     <t>阴性名词；复数iglesias；搭配：la iglesia教堂</t>
@@ -1365,13 +1278,13 @@
     <t>梦想</t>
   </si>
   <si>
-    <t>sueño（原形）</t>
-  </si>
-  <si>
-    <t>经济衡量万物的价格，文学探索其价值，而人类的梦想便栖息于此间的裂隙</t>
-  </si>
-  <si>
-    <t>La economía mide el precio de las cosas, la literatura explora su valor, y en esa brecha habita el sueno humano de una vida con sentido</t>
+    <t>sueño（原形） | 阳性: Sueno | 阴性: Suena</t>
+  </si>
+  <si>
+    <t>经济衡量万物的价格，文学探索其价值，而人类的梦想便栖息于此间的裂隙。</t>
+  </si>
+  <si>
+    <t>La economía mide el precio de las cosas, la literatura explora su valor, y en esa brecha habita el sueno humano de una vida con sentido.</t>
   </si>
   <si>
     <t>阳性名词；复数sueños；搭配：un sueño梦想</t>
@@ -1386,10 +1299,10 @@
     <t>economía（原形）</t>
   </si>
   <si>
-    <t>经济衡量万物的价格</t>
-  </si>
-  <si>
-    <t>La economía mide el precio de las cosas</t>
+    <t>经济衡量万物的价格。</t>
+  </si>
+  <si>
+    <t>La economía mide el precio de las cosas.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la economía经济</t>
@@ -1404,10 +1317,10 @@
     <t>literatura（原形）</t>
   </si>
   <si>
-    <t>文学探索其价值</t>
-  </si>
-  <si>
-    <t>la literatura explora su valor</t>
+    <t>他文学探索其价值。</t>
+  </si>
+  <si>
+    <t>Él la literatura explora su valor.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la literatura文学</t>
@@ -1422,10 +1335,10 @@
     <t>cara（原形）</t>
   </si>
   <si>
-    <t>天空见证着青丝如何染上银霜，脸庞如何刻上皱纹</t>
-  </si>
-  <si>
-    <t>EI cielo testigo como el cabello se tine de plata y la cara se pinta de arrugas</t>
+    <t>他天空见证着青丝如何染上银霜，脸庞如何刻上皱纹。</t>
+  </si>
+  <si>
+    <t>El cielo testigo como el cabello se tine de plata y la cara se pinta de arrugas.</t>
   </si>
   <si>
     <t>阴性名词；复数caras；搭配：la cara脸</t>
@@ -1437,13 +1350,13 @@
     <t>头发</t>
   </si>
   <si>
-    <t>cabello（原形）</t>
-  </si>
-  <si>
-    <t>天空见证着青丝如何染上银霜</t>
-  </si>
-  <si>
-    <t>EI cielo testigo como el cabello se tine de plata</t>
+    <t>cabello（原形） | 阳性: Cabello | 阴性: Cabella</t>
+  </si>
+  <si>
+    <t>他天空见证着青丝如何染上银霜。</t>
+  </si>
+  <si>
+    <t>El cielo testigo como el cabello se tine de plata.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：el cabello头发</t>
@@ -1455,13 +1368,13 @@
     <t>天空</t>
   </si>
   <si>
-    <t>cielo（原形）</t>
-  </si>
-  <si>
-    <t>诉说着一段丰盛生命的故事</t>
-  </si>
-  <si>
-    <t>contando historias de una vida bien vivida</t>
+    <t>cielo（原形） | 阳性: Cielo | 阴性: Ciela</t>
+  </si>
+  <si>
+    <t>他诉说着一段丰盛生命的故事。</t>
+  </si>
+  <si>
+    <t>Él contando historias de una vida bien vivida.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：el cielo天空</t>
@@ -1476,10 +1389,10 @@
     <t>vista（原形）</t>
   </si>
   <si>
-    <t>没人会问你口袋里曾装着什么，只会问你视野中珍藏了怎样的风景</t>
-  </si>
-  <si>
-    <t>no preguntaran qué llevaste en el bolsillo, sino qué paisajes guardaste en tu vista</t>
+    <t>没人会问你口袋里曾装着什么，只会问你视野中珍藏了怎样的风景。</t>
+  </si>
+  <si>
+    <t>Él no preguntaran qué llevaste en el bolsillo, sino qué paisajes guardaste en tu vista.</t>
   </si>
   <si>
     <t>阴性名词；复数vistas；搭配：la vista视野</t>
@@ -1491,13 +1404,13 @@
     <t>口袋</t>
   </si>
   <si>
-    <t>bolsillo（原形）</t>
-  </si>
-  <si>
-    <t>没人会问你口袋里曾装着什么</t>
-  </si>
-  <si>
-    <t>no preguntaran qué llevaste en el bolsillo</t>
+    <t>bolsillo（原形） | 阳性: Bolsillo | 阴性: Bolsilla</t>
+  </si>
+  <si>
+    <t>没人会问你口袋里曾装着什么。</t>
+  </si>
+  <si>
+    <t>Él no preguntaran qué llevaste en el bolsillo.</t>
   </si>
   <si>
     <t>阳性名词；复数bolsillos；搭配：el bolsillo口袋</t>
@@ -1509,13 +1422,13 @@
     <t>心</t>
   </si>
   <si>
-    <t>corazón（原形）</t>
-  </si>
-  <si>
-    <t>以及心中存留着怎样的爱</t>
-  </si>
-  <si>
-    <t>y qué amor en tu corazón</t>
+    <t>corazón（原形） | 阳性: Corazón | 阴性: Corazna</t>
+  </si>
+  <si>
+    <t>他以及心中存留着怎样的爱。</t>
+  </si>
+  <si>
+    <t>Él y qué amor en tu corazón.</t>
   </si>
   <si>
     <t>阳性名词；复数corazones；搭配：el corazón心</t>
@@ -1527,13 +1440,13 @@
     <t>风格</t>
   </si>
   <si>
-    <t>estilo（原形）</t>
-  </si>
-  <si>
-    <t>正义不只是一纸判决，更是一种体现在每日与他人交谈中的生活方式</t>
-  </si>
-  <si>
-    <t>La justicia no es solo un veredicto, es un estilo de vida que se practica en cada conversación cotidiana con los demas</t>
+    <t>estilo（原形） | 阳性: Estilo | 阴性: Estila</t>
+  </si>
+  <si>
+    <t>正义不只是一纸判决，更是一种体现在每日与他人交谈中的生活方式。</t>
+  </si>
+  <si>
+    <t>La justicia no es solo un veredicto, es un estilo de vida que se practica en cada conversación cotidiana con los demas.</t>
   </si>
   <si>
     <t>阳性名词；复数estilos；搭配：el estilo风格</t>
@@ -1548,10 +1461,10 @@
     <t>justicia（原形）</t>
   </si>
   <si>
-    <t>正义不只是一纸判决</t>
-  </si>
-  <si>
-    <t>La justicia no es solo un veredicto</t>
+    <t>他正义不只是一纸判决。</t>
+  </si>
+  <si>
+    <t>La justicia no es solo un veredicto.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la justicia正义</t>
@@ -1563,13 +1476,13 @@
     <t>对话</t>
   </si>
   <si>
-    <t>conversación（原形）</t>
-  </si>
-  <si>
-    <t>更是一种体现在每日与他人交谈中的生活方式</t>
-  </si>
-  <si>
-    <t>es un estilo de vida que se practica en cada conversación cotidiana con los demas</t>
+    <t>conversación（原形） | 阳性: Conversación | 阴性: Conversacina</t>
+  </si>
+  <si>
+    <t>更是一种体现在每日与他人交谈中的生活方式。</t>
+  </si>
+  <si>
+    <t>Él es un estilo de vida que se practica en cada conversación cotidiana con los demas.</t>
   </si>
   <si>
     <t>阴性名词；复数conversaciones；搭配：una conversación对话</t>
@@ -1584,10 +1497,10 @@
     <t>paz（原形）</t>
   </si>
   <si>
-    <t>历史向我们展示了千百种发动战争的方式，却只给出了寥寥几种构建和平的途径</t>
-  </si>
-  <si>
-    <t>La historia nos muestra mil maneras de hacer la guerra, y apenas unas pocas de construir la paz</t>
+    <t>历史向我们展示了千百种发动战争的方式，却只给出了寥寥几种构建和平的途径。</t>
+  </si>
+  <si>
+    <t>La historia nos muestra mil maneras de hacer la guerra, y apenas unas pocas de construir la paz.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la paz和平</t>
@@ -1602,10 +1515,10 @@
     <t>guerra（原形）</t>
   </si>
   <si>
-    <t>历史向我们展示了千百种发动战争的方式</t>
-  </si>
-  <si>
-    <t>La historia nos muestra mil maneras de hacer la guerra</t>
+    <t>历史向我们展示了千百种发动战争的方式。</t>
+  </si>
+  <si>
+    <t>La historia nos muestra mil maneras de hacer la guerra.</t>
   </si>
   <si>
     <t>阴性名词；复数guerras；搭配：la guerra战争</t>
@@ -1614,18 +1527,9 @@
     <t>Manera</t>
   </si>
   <si>
-    <t>方式</t>
-  </si>
-  <si>
     <t>manera（原形）</t>
   </si>
   <si>
-    <t>历史向我们展示了千百种发动战争的方式</t>
-  </si>
-  <si>
-    <t>La historia nos muestra mil maneras de hacer la guerra</t>
-  </si>
-  <si>
     <t>阴性名词；复数maneras；搭配：de esta manera用这种方式</t>
   </si>
   <si>
@@ -1635,13 +1539,13 @@
     <t>教育</t>
   </si>
   <si>
-    <t>educación（原形）</t>
-  </si>
-  <si>
-    <t>最好的工作，源于你所爱，并运用教育所予</t>
-  </si>
-  <si>
-    <t>El mejor trabajo es aquel que nace de lo que amas y utiliza lo que la educación te dio</t>
+    <t>educación（原形） | 阳性: Educación | 阴性: Educacina</t>
+  </si>
+  <si>
+    <t>最好的工作，源于你所爱，并运用教育所予。</t>
+  </si>
+  <si>
+    <t>El mejor trabajo es aquel que nace de lo que amas y utiliza lo que la educación te dio.</t>
   </si>
   <si>
     <t>阴性名词；不可数；搭配：la educación教育</t>
@@ -1653,33 +1557,18 @@
     <t>爱</t>
   </si>
   <si>
-    <t>amor（原形）</t>
-  </si>
-  <si>
-    <t>最好的工作，源于你所爱</t>
-  </si>
-  <si>
-    <t>El mejor trabajo es aquel que nace de lo que amas</t>
+    <t>amor（原形） | 阳性: Amor | 阴性: Amora</t>
+  </si>
+  <si>
+    <t>最好的工作，源于你所爱。</t>
+  </si>
+  <si>
+    <t>El mejor trabajo es aquel que nace de lo que amas.</t>
   </si>
   <si>
     <t>阳性名词；不可数；搭配：el amor爱</t>
   </si>
   <si>
-    <t>Trabajo</t>
-  </si>
-  <si>
-    <t>工作</t>
-  </si>
-  <si>
-    <t>trabajo（原形）</t>
-  </si>
-  <si>
-    <t>最好的工作，源于你所爱</t>
-  </si>
-  <si>
-    <t>El mejor trabajo es aquel que nace de lo que amas</t>
-  </si>
-  <si>
     <t>阳性名词；复数trabajos；搭配：el trabajo工作</t>
   </si>
   <si>
@@ -1692,10 +1581,10 @@
     <t>dólar（原形）</t>
   </si>
   <si>
-    <t>在城市中心，金融项目的摩天大楼随着美元的节奏跳动</t>
-  </si>
-  <si>
-    <t>En el centro de la ciudad, el rascacielos del programa financiero late al ritmo del dólar</t>
+    <t>他在城市中心，金融项目的摩天大楼随着美元的节奏跳动。</t>
+  </si>
+  <si>
+    <t>Él En el centro de la ciudad, el rascacielos del programa financiero late al ritmo del dólar.</t>
   </si>
   <si>
     <t>阳性名词；复数dólares；搭配：el dólar美元</t>
@@ -1707,13 +1596,13 @@
     <t>中心</t>
   </si>
   <si>
-    <t>centro（原形）</t>
-  </si>
-  <si>
-    <t>在城市中心</t>
-  </si>
-  <si>
-    <t>En el centro de la ciudad</t>
+    <t>centro（原形） | 阳性: Centro | 阴性: Centra</t>
+  </si>
+  <si>
+    <t>他在城市中心。</t>
+  </si>
+  <si>
+    <t>Él En el centro de la ciudad.</t>
   </si>
   <si>
     <t>阳性名词；复数centros；搭配：el centro中心</t>
@@ -1728,10 +1617,10 @@
     <t>programa（原形）</t>
   </si>
   <si>
-    <t>金融项目的摩天大楼随着美元的节奏跳动</t>
-  </si>
-  <si>
-    <t>el rascacielos del programa financiero late al ritmo del dólar</t>
+    <t>他金融项目的摩天大楼随着美元的节奏跳动。</t>
+  </si>
+  <si>
+    <t>El rascaciElos dEl programa financiero late al ritmo dEl dólar.</t>
   </si>
   <si>
     <t>阳性名词；复数programas；搭配：un programa计划</t>
@@ -1750,16 +1639,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1813,19 +1702,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1862,7 +1751,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="luEWAS">
+        <xdr:cNvPr id="2" name="Picture 2" descr="sPBqvd">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
@@ -2190,11 +2079,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D552FC3E-E9DE-4A35-B13A-6FB2F18E353D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1AF27E1-65D1-4C91-9319-CFA59BB4FD59}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2225,1882 +2114,1902 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>385</v>
+        <v>109</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>414</v>
+        <v>216</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>415</v>
+        <v>217</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>416</v>
+        <v>218</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>419</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>425</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>456</v>
+        <v>421</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>457</v>
+        <v>422</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>461</v>
+        <v>426</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>479</v>
+        <v>444</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>490</v>
+        <v>455</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>506</v>
+        <v>471</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>509</v>
+        <v>474</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>511</v>
+        <v>476</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>512</v>
+        <v>477</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>517</v>
+        <v>482</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>521</v>
+        <v>486</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>523</v>
+        <v>488</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>526</v>
+        <v>491</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>527</v>
+        <v>492</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>530</v>
+        <v>495</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>531</v>
+        <v>496</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>533</v>
+        <v>498</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>535</v>
+        <v>197</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>536</v>
+        <v>500</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>548</v>
+        <v>510</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>550</v>
+        <v>512</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>551</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>552</v>
+        <v>42</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>553</v>
+        <v>43</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>554</v>
+        <v>44</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>556</v>
+        <v>512</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>557</v>
+        <v>514</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>558</v>
+        <v>515</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>560</v>
+        <v>517</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>563</v>
+        <v>520</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>564</v>
+        <v>521</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>565</v>
+        <v>522</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>566</v>
+        <v>523</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>567</v>
+        <v>524</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>569</v>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>527</v>
+      </c>
+      <c r="B96" t="s">
+        <v>528</v>
+      </c>
+      <c r="C96" t="s">
+        <v>529</v>
+      </c>
+      <c r="D96" t="s">
+        <v>530</v>
+      </c>
+      <c r="E96" t="s">
+        <v>531</v>
+      </c>
+      <c r="F96" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
